--- a/sheets/대금율보/검수/대풍류 반염불.xlsx
+++ b/sheets/대금율보/검수/대풍류 반염불.xlsx
@@ -1934,24 +1934,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="143.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="143.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="143.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="M5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="143.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="143.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="M7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="143.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2243,6 +2243,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>